--- a/nr-add-examples/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T08:08:00+00:00</t>
+    <t>2025-05-12T08:18:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T08:18:40+00:00</t>
+    <t>2025-05-12T08:26:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T08:26:30+00:00</t>
+    <t>2025-05-12T09:15:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T09:15:35+00:00</t>
+    <t>2025-05-12T09:44:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -279,7 +279,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}fr-core-1:If identityReliability status = 'VALI', then at least Patient.identifier[INS-NIR] or Patient.identifier[INS-NIA] or Patient.identifier[INS-NIR-TEST]or Patient.identifier[INS-NIR-DEMO] SHALL be present {(extension.where(url= 'https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension.where(url = 'identityStatus').value.code = 'VALI') implies (identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.8').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.9').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.10').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.11').exists())}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}fr-core-1:If identityReliability status = 'VALI', then at least Patient.identifier[INS-NIR] or Patient.identifier[INS-NIA] or Patient.identifier[INS-NIR-TEST]or Patient.identifier[INS-NIR-DEMO] SHALL be present {(extension('https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension(url'identityStatus').value.code = 'VALI') implies (identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.8').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.9').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.10').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.11').exists())}</t>
   </si>
   <si>
     <t>Patient[classCode=PAT]</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T09:44:35+00:00</t>
+    <t>2025-05-12T09:48:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -279,7 +279,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}fr-core-1:If identityReliability status = 'VALI', then at least Patient.identifier[INS-NIR] or Patient.identifier[INS-NIA] or Patient.identifier[INS-NIR-TEST]or Patient.identifier[INS-NIR-DEMO] SHALL be present {(extension('https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension(url'identityStatus').value.code = 'VALI') implies (identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.8').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.9').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.10').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.11').exists())}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}fr-core-1:If identityReliability status = 'VALI', then at least Patient.identifier[INS-NIR] or Patient.identifier[INS-NIA] or Patient.identifier[INS-NIR-TEST]or Patient.identifier[INS-NIR-DEMO] SHALL be present {(extension('https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension('identityStatus').value.code = 'VALI') implies (identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.8').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.9').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.10').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.11').exists())}</t>
   </si>
   <si>
     <t>Patient[classCode=PAT]</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T09:48:13+00:00</t>
+    <t>2025-05-12T10:07:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -279,7 +279,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}fr-core-1:If identityReliability status = 'VALI', then at least Patient.identifier[INS-NIR] or Patient.identifier[INS-NIA] or Patient.identifier[INS-NIR-TEST]or Patient.identifier[INS-NIR-DEMO] SHALL be present {(extension('https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension('identityStatus').value.code = 'VALI') implies (identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.8').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.9').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.10').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.11').exists())}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}fr-core-1:If identityReliability status = 'VALI', then at least Patient.identifier[INS-NIR] or Patient.identifier[INS-NIA] or Patient.identifier[INS-NIR-TEST] or Patient.identifier[INS-NIR-DEMO] SHALL be present {(extension.exists('https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension.exists('identityStatus').value.code = 'VALI') implies (identifier.exists(system = 'urn:oid:1.2.250.1.213.1.4.8') or identifier.exists(system = 'urn:oid:1.2.250.1.213.1.4.9') or identifier.exists(system = 'urn:oid:1.2.250.1.213.1.4.10') or identifier.exists(system = 'urn:oid:1.2.250.1.213.1.4.11'))}</t>
   </si>
   <si>
     <t>Patient[classCode=PAT]</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T10:07:46+00:00</t>
+    <t>2025-05-12T12:08:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T12:08:59+00:00</t>
+    <t>2025-05-12T12:21:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T12:21:25+00:00</t>
+    <t>2025-05-12T12:41:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -279,7 +279,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}fr-core-1:If identityReliability status = 'VALI', then at least Patient.identifier[INS-NIR] or Patient.identifier[INS-NIA] or Patient.identifier[INS-NIR-TEST] or Patient.identifier[INS-NIR-DEMO] SHALL be present {(extension.exists('https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension.exists('identityStatus').value.code = 'VALI') implies (identifier.exists(system = 'urn:oid:1.2.250.1.213.1.4.8') or identifier.exists(system = 'urn:oid:1.2.250.1.213.1.4.9') or identifier.exists(system = 'urn:oid:1.2.250.1.213.1.4.10') or identifier.exists(system = 'urn:oid:1.2.250.1.213.1.4.11'))}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}fr-core-1:If identityReliability status = 'VALI', then at least Patient.identifier[INS-NIR] or Patient.identifier[INS-NIA] or Patient.identifier[INS-NIR-TEST] or Patient.identifier[INS-NIR-DEMO] SHALL be present {(extension.where(url = 'https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension.where(url = 'identityStatus').value.code = 'VALI') implies (identifier.exists(system = 'urn:oid:1.2.250.1.213.1.4.8') or identifier.exists(system = 'urn:oid:1.2.250.1.213.1.4.9') or identifier.exists(system = 'urn:oid:1.2.250.1.213.1.4.10') or identifier.exists(system = 'urn:oid:1.2.250.1.213.1.4.11'))}</t>
   </si>
   <si>
     <t>Patient[classCode=PAT]</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T12:41:16+00:00</t>
+    <t>2025-05-12T13:04:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -279,7 +279,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}fr-core-1:If identityReliability status = 'VALI', then at least Patient.identifier[INS-NIR] or Patient.identifier[INS-NIA] or Patient.identifier[INS-NIR-TEST] or Patient.identifier[INS-NIR-DEMO] SHALL be present {(extension.where(url = 'https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension.where(url = 'identityStatus').value.code = 'VALI') implies (identifier.exists(system = 'urn:oid:1.2.250.1.213.1.4.8') or identifier.exists(system = 'urn:oid:1.2.250.1.213.1.4.9') or identifier.exists(system = 'urn:oid:1.2.250.1.213.1.4.10') or identifier.exists(system = 'urn:oid:1.2.250.1.213.1.4.11'))}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}fr-core-1:If identityReliability status = 'VALI', then at least Patient.identifier[INS-NIR] or Patient.identifier[INS-NIA] or Patient.identifier[INS-NIR-TEST]or Patient.identifier[INS-NIR-DEMO] SHALL be present {(extension('https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension('identityStatus').value.code = 'VALI') implies (identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.8').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.9').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.10').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.11').exists())}</t>
   </si>
   <si>
     <t>Patient[classCode=PAT]</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T13:04:33+00:00</t>
+    <t>2025-05-12T14:29:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T14:29:06+00:00</t>
+    <t>2025-05-12T14:37:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T14:37:35+00:00</t>
+    <t>2025-05-12T15:04:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -279,7 +279,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}fr-core-1:If identityReliability status = 'VALI', then at least Patient.identifier[INS-NIR] or Patient.identifier[INS-NIA] or Patient.identifier[INS-NIR-TEST]or Patient.identifier[INS-NIR-DEMO] SHALL be present {(extension('https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension('identityStatus').value.code = 'VALI') implies (identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.8').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.9').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.10').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.11').exists())}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}fr-core-1:If identityReliability status = 'VALI', then at least Patient.identifier[INS-NIR] or Patient.identifier[INS-NIA] or Patient.identifier[INS-NIR-TEST]or Patient.identifier[INS-NIR-DEMO] SHALL be present {(extension('https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension('identityStatus').value.exists(code = 'VALI')) implies (identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.8').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.9').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.10').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.11').exists())}</t>
   </si>
   <si>
     <t>Patient[classCode=PAT]</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T15:04:22+00:00</t>
+    <t>2025-05-13T10:20:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T10:20:58+00:00</t>
+    <t>2025-05-20T13:44:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:46:53+00:00</t>
+    <t>2025-05-20T13:54:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:54:28+00:00</t>
+    <t>2025-05-20T13:56:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:56:00+00:00</t>
+    <t>2025-05-23T16:42:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T16:42:05+00:00</t>
+    <t>2025-05-23T16:51:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T16:51:26+00:00</t>
+    <t>2025-05-24T07:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-24T07:13:38+00:00</t>
+    <t>2025-05-26T07:36:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-26T07:36:52+00:00</t>
+    <t>2025-05-28T11:10:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
